--- a/dataset_t6_grouped/results2/G1/G1_T0374L_W0041F0003T0006Z000C1N5_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T0374L_W0041F0003T0006Z000C1N5_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>2.885629837440435</v>
+        <v>0.4689148485840706</v>
       </c>
       <c r="D2" t="n">
-        <v>2.597028606031716</v>
+        <v>0.4220171484801539</v>
       </c>
       <c r="E2" t="n">
-        <v>13.78171818547022</v>
+        <v>2.239529205138912</v>
       </c>
       <c r="F2" t="n">
-        <v>13.51940161553427</v>
+        <v>2.196902762524318</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>15.95204433694392</v>
+        <v>2.592207204753386</v>
       </c>
       <c r="D3" t="n">
-        <v>15.4823683740721</v>
+        <v>2.515884860786716</v>
       </c>
       <c r="E3" t="n">
-        <v>13.78171818547022</v>
+        <v>2.239529205138912</v>
       </c>
       <c r="F3" t="n">
-        <v>13.51940161553427</v>
+        <v>2.196902762524318</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>41.31607077266134</v>
+        <v>6.713861500557468</v>
       </c>
       <c r="D4" t="n">
-        <v>40.89364519717993</v>
+        <v>6.645217344541739</v>
       </c>
       <c r="E4" t="n">
-        <v>13.78171818547022</v>
+        <v>2.239529205138912</v>
       </c>
       <c r="F4" t="n">
-        <v>13.51940161553427</v>
+        <v>2.196902762524318</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>23.57019634321902</v>
+        <v>3.83015690577309</v>
       </c>
       <c r="D5" t="n">
-        <v>23.24077218780657</v>
+        <v>3.776625480518567</v>
       </c>
       <c r="E5" t="n">
-        <v>13.78171818547022</v>
+        <v>2.239529205138912</v>
       </c>
       <c r="F5" t="n">
-        <v>13.51940161553427</v>
+        <v>2.196902762524318</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>6.067568438462794</v>
+        <v>0.985979871250204</v>
       </c>
       <c r="D6" t="n">
-        <v>7.100901748055244</v>
+        <v>1.153896534058977</v>
       </c>
       <c r="E6" t="n">
-        <v>13.78171818547022</v>
+        <v>2.239529205138912</v>
       </c>
       <c r="F6" t="n">
-        <v>13.51940161553427</v>
+        <v>2.196902762524318</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
